--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99639</v>
+        <v>99645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 1017-2025 artfynd.xlsx
+++ b/artfynd/S 1017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483095</v>
       </c>
       <c r="B2" t="n">
-        <v>99645</v>
+        <v>99649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
